--- a/diseases/d031/2020-2025.xlsx
+++ b/diseases/d031/2020-2025.xlsx
@@ -1288,9 +1288,6 @@
       <c r="O5" t="n">
         <v>562</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.083718581308633</v>
       </c>
@@ -1959,9 +1956,6 @@
       <c r="O9" t="n">
         <v>456</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.8793161442646561</v>
       </c>
@@ -2630,9 +2624,6 @@
       <c r="O13" t="n">
         <v>224</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.4319447726212345</v>
       </c>
@@ -3301,9 +3292,6 @@
       <c r="O17" t="n">
         <v>158</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.3046753306881922</v>
       </c>
@@ -3972,9 +3960,6 @@
       <c r="O21" t="n">
         <v>170</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.3278152292214727</v>
       </c>
@@ -4643,9 +4628,6 @@
       <c r="O25" t="n">
         <v>141</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.271893807766045</v>
       </c>
@@ -5314,9 +5296,6 @@
       <c r="O29" t="n">
         <v>137</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.2641805082549515</v>
       </c>
@@ -5985,9 +5964,6 @@
       <c r="O33" t="n">
         <v>133</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.256467208743858</v>
       </c>
@@ -6656,9 +6632,6 @@
       <c r="O37" t="n">
         <v>93</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.1793342136329233</v>
       </c>
@@ -7327,9 +7300,6 @@
       <c r="O41" t="n">
         <v>91</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.1754775638773766</v>
       </c>
@@ -7998,9 +7968,6 @@
       <c r="O45" t="n">
         <v>68</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.1311260916885891</v>
       </c>
@@ -8669,9 +8636,6 @@
       <c r="O49" t="n">
         <v>67</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.1291977668108157</v>
       </c>
@@ -9113,9 +9077,6 @@
       <c r="O52" t="n">
         <v>67</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.1292228944973661</v>
       </c>
@@ -9557,9 +9518,6 @@
       <c r="O55" t="n">
         <v>59</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.113793295154397</v>
       </c>
@@ -10001,9 +9959,6 @@
       <c r="O58" t="n">
         <v>74</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.142723793922464</v>
       </c>
@@ -10445,9 +10400,6 @@
       <c r="O61" t="n">
         <v>58</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.1118645952365259</v>
       </c>
@@ -10889,9 +10841,6 @@
       <c r="O64" t="n">
         <v>62</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.1195793949080104</v>
       </c>
@@ -11333,9 +11282,6 @@
       <c r="O67" t="n">
         <v>41</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.07907669663271656</v>
       </c>
@@ -11777,9 +11723,6 @@
       <c r="O70" t="n">
         <v>85</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.1639394930190466</v>
       </c>
@@ -12221,9 +12164,6 @@
       <c r="O73" t="n">
         <v>69</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.1330802943331084</v>
       </c>
@@ -12665,9 +12605,6 @@
       <c r="O76" t="n">
         <v>49</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.09450629597568565</v>
       </c>
@@ -13109,9 +13046,6 @@
       <c r="O79" t="n">
         <v>41</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.07907669663271656</v>
       </c>
@@ -13553,9 +13487,6 @@
       <c r="O82" t="n">
         <v>33</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.06364709728974749</v>
       </c>
@@ -13997,9 +13928,6 @@
       <c r="O85" t="n">
         <v>40</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.07714799671484543</v>
       </c>
@@ -14441,9 +14369,6 @@
       <c r="O88" t="n">
         <v>38</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.07338384890813958</v>
       </c>
@@ -14885,9 +14810,6 @@
       <c r="O91" t="n">
         <v>31</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.05986577147769281</v>
       </c>
@@ -15329,9 +15251,6 @@
       <c r="O94" t="n">
         <v>30</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.05793461755905756</v>
       </c>
@@ -15773,9 +15692,6 @@
       <c r="O97" t="n">
         <v>24</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.04634769404724604</v>
       </c>
@@ -16217,9 +16133,6 @@
       <c r="O100" t="n">
         <v>41</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.07917731066404533</v>
       </c>
@@ -16661,9 +16574,6 @@
       <c r="O103" t="n">
         <v>45</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.08690192633858634</v>
       </c>
@@ -17105,9 +17015,6 @@
       <c r="O106" t="n">
         <v>56</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.1081446194435741</v>
       </c>
@@ -17549,9 +17456,6 @@
       <c r="O109" t="n">
         <v>61</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.1178003890367504</v>
       </c>
@@ -17993,9 +17897,6 @@
       <c r="O112" t="n">
         <v>47</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.09076423417585684</v>
       </c>
@@ -18437,9 +18338,6 @@
       <c r="O115" t="n">
         <v>45</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.08690192633858634</v>
       </c>
@@ -18881,9 +18779,6 @@
       <c r="O118" t="n">
         <v>43</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.08303961850131585</v>
       </c>
@@ -19325,9 +19220,6 @@
       <c r="O121" t="n">
         <v>44</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.08497077241995109</v>
       </c>
@@ -19769,9 +19661,6 @@
       <c r="O124" t="n">
         <v>35</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.06763449830149484</v>
       </c>
@@ -20213,9 +20102,6 @@
       <c r="O127" t="n">
         <v>36</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.06956691253868041</v>
       </c>
@@ -20657,9 +20543,6 @@
       <c r="O130" t="n">
         <v>38</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.07343174101305154</v>
       </c>
@@ -21101,9 +20984,6 @@
       <c r="O133" t="n">
         <v>53</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.1024179545708351</v>
       </c>
@@ -21545,9 +21425,6 @@
       <c r="O136" t="n">
         <v>56</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.1082151972823917</v>
       </c>
@@ -21989,9 +21866,6 @@
       <c r="O139" t="n">
         <v>62</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.1198096827055051</v>
       </c>
@@ -22433,9 +22307,6 @@
       <c r="O142" t="n">
         <v>95</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.1835793525326289</v>
       </c>
@@ -22877,9 +22748,6 @@
       <c r="O145" t="n">
         <v>67</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.129471753891433</v>
       </c>
@@ -23321,9 +23189,6 @@
       <c r="O148" t="n">
         <v>56</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.1082151972823917</v>
       </c>
@@ -23765,9 +23630,6 @@
       <c r="O151" t="n">
         <v>76</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.1468634820261031</v>
       </c>
@@ -24209,9 +24071,6 @@
       <c r="O154" t="n">
         <v>88</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.1700524528723299</v>
       </c>
@@ -24653,9 +24512,6 @@
       <c r="O157" t="n">
         <v>153</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.2956593782893918</v>
       </c>
@@ -25097,9 +24953,6 @@
       <c r="O160" t="n">
         <v>162</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.3132396540519386</v>
       </c>
@@ -25541,9 +25394,6 @@
       <c r="O163" t="n">
         <v>150</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.2900367167147579</v>
       </c>
@@ -25985,9 +25835,6 @@
       <c r="O166" t="n">
         <v>226</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.4369886531835687</v>
       </c>
@@ -26429,9 +26276,6 @@
       <c r="O169" t="n">
         <v>386</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.7463611510126439</v>
       </c>
@@ -26873,9 +26717,6 @@
       <c r="O172" t="n">
         <v>784</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>1.515925239362468</v>
       </c>
@@ -27317,9 +27158,6 @@
       <c r="O175" t="n">
         <v>979</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>1.892972971091654</v>
       </c>
@@ -27761,9 +27599,6 @@
       <c r="O178" t="n">
         <v>972</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>1.879437924311632</v>
       </c>
@@ -28205,9 +28040,6 @@
       <c r="O181" t="n">
         <v>432</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.835305744138503</v>
       </c>
@@ -28649,9 +28481,6 @@
       <c r="O184" t="n">
         <v>465</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.8991138218157498</v>
       </c>
@@ -29093,9 +28922,6 @@
       <c r="O187" t="n">
         <v>465</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.8991138218157498</v>
       </c>
@@ -29537,9 +29363,6 @@
       <c r="O190" t="n">
         <v>666</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>1.287763022213525</v>
       </c>
@@ -29981,9 +29804,6 @@
       <c r="O193" t="n">
         <v>955</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>1.846567096417292</v>
       </c>
@@ -30425,9 +30245,6 @@
       <c r="O196" t="n">
         <v>601</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>1.163217637661945</v>
       </c>
@@ -30869,9 +30686,6 @@
       <c r="O199" t="n">
         <v>514</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.9948317233914135</v>
       </c>
@@ -31313,9 +31127,6 @@
       <c r="O202" t="n">
         <v>692</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>1.339345433048362</v>
       </c>
@@ -31757,9 +31568,6 @@
       <c r="O205" t="n">
         <v>987</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>1.910309165344991</v>
       </c>
@@ -32201,9 +32009,6 @@
       <c r="O208" t="n">
         <v>1470</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>2.845141310088283</v>
       </c>
@@ -32645,9 +32450,6 @@
       <c r="O211" t="n">
         <v>2120</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>4.103196991419837</v>
       </c>
@@ -33089,9 +32891,6 @@
       <c r="O214" t="n">
         <v>1814</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>3.510943086054521</v>
       </c>
@@ -33533,9 +33332,6 @@
       <c r="O217" t="n">
         <v>937</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>1.813535651396409</v>
       </c>
@@ -33977,9 +33773,6 @@
       <c r="O220" t="n">
         <v>1005</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>1.94514763036648</v>
       </c>
@@ -34421,9 +34214,6 @@
       <c r="O223" t="n">
         <v>680</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>1.316119789700703</v>
       </c>
@@ -34865,9 +34655,6 @@
       <c r="O226" t="n">
         <v>933</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>1.805793770280523</v>
       </c>
@@ -35308,9 +35095,6 @@
       </c>
       <c r="O229" t="n">
         <v>1360</v>
-      </c>
-      <c r="Q229" t="n">
-        <v>0</v>
       </c>
       <c r="R229" t="n">
         <v>2.632239579401405</v>
